--- a/output/2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -497,7 +497,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Produttore/distributore di dust collector, blower fan, pneumatic/screw conveyor, ductwork, bagging/batching plant, bucket elevator, rotary valve; esporta in Thailandia, Corea, UK, Canada, Indonesia. Esistenza confermata su directory B2B (exporthub, eco-web); sito ufficiale e contatti diretti non reperiti con fonte affidabile.</t>
+          <t>Produttore/distributore di dust collector, blower fan, pneumatic/screw conveyor, ductwork, bagging/batching plant, bucket elevator, rotary valve; esporta in Thailandia, Corea, UK, Canada, Indonesia. Esistenza confermata su directory B2B (exporthub, eco-web); sito ufficiale e contatti diretti non reperiti con fonte affidabile. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -535,7 +535,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Sede regionale APAC di AAF, leader mondiale filtrazione aria; produce filtri HVAC, cleanroom e filtrazione industriale. Esistenza e contatti confermati via ricerca web (indirizzo e telefono riscontrati su fonti multiple).</t>
+          <t>Sede regionale APAC di AAF, leader mondiale filtrazione aria; produce filtri HVAC, cleanroom e filtrazione industriale. Esistenza e contatti confermati via ricerca web (indirizzo e telefono riscontrati su fonti multiple). [DUPLICATO — vedi anche: 2026-10-04_20_Malesia_Selangor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Ingegneria/produzione impianti controllo inquinamento aria industriale: dust collector, scrubber, filtrazione, ventilazione industriale. Oltre 1000 installazioni Malesia/ASEAN, ISO 9001:2015. Confermato tramite sito ufficiale (fetch diretto).</t>
+          <t>Ingegneria/produzione impianti controllo inquinamento aria industriale: dust collector, scrubber, filtrazione, ventilazione industriale. Oltre 1000 installazioni Malesia/ASEAN, ISO 9001:2015. Confermato tramite sito ufficiale (fetch diretto). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Dal 1986, distributore/importatore/agente di macchine utensili di precisione: CNC lathe, machining center, grinder, EDM wire cut, fresatrici. Esistenza e indirizzo confermati via ricerca web; sito/contatti diretti non reperiti.</t>
+          <t>Dal 1986, distributore/importatore/agente di macchine utensili di precisione: CNC lathe, machining center, grinder, EDM wire cut, fresatrici. Esistenza e indirizzo confermati via ricerca web; sito/contatti diretti non reperiti. [DUPLICATO — vedi anche: 2026-10-04_14_Malesia_Pulau_Pinang_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Produttore/distributore di ventole, air handling units e prodotti per ventilazione industriale; quasi 50 anni di presenza globale. Confermato tramite sito ufficiale (fetch diretto, redirect da systemair.my).</t>
+          <t>Produttore/distributore di ventole, air handling units e prodotti per ventilazione industriale; quasi 50 anni di presenza globale. Confermato tramite sito ufficiale (fetch diretto, redirect da systemair.my). [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Macchine sabbiatura standard/custom, dust collector industriali, macchine deflashing plastica, materiali abrasivi. Esistenza e indirizzo confermati via ricerca web; sito/contatti diretti non reperiti.</t>
+          <t>Macchine sabbiatura standard/custom, dust collector industriali, macchine deflashing plastica, materiali abrasivi. Esistenza e indirizzo confermati via ricerca web; sito/contatti diretti non reperiti. [DUPLICATO — vedi anche: 2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
